--- a/templates/qa_template.xlsx
+++ b/templates/qa_template.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="10.6875" customWidth="1" style="1" min="2" max="2"/>
@@ -1126,18 +1126,13 @@
           <t>质检会话占比</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="11" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="11" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="11" t="n"/>
-      <c r="R1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="11" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1182,18 +1177,13 @@
       <c r="J2" s="7" t="n">
         <v>0.52</v>
       </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>新版/老版</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="11" t="n"/>
-      <c r="R2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
